--- a/Modules/iVCA/iVCA_BOM.xlsx
+++ b/Modules/iVCA/iVCA_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\iVCA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73C06C4-3A69-47D3-9ACC-ACB060397DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA5689F-4212-4F7B-A3EC-BF71F712E617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -119,15 +119,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Jack Nut</t>
   </si>
   <si>
@@ -479,9 +473,6 @@
     <t>https://www.tme.eu/de/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>https://www.tme.eu/de/en/details/icvt-14p/standard-dip-sockets/connfly/ds1009-14at1nx-0a2/</t>
   </si>
   <si>
@@ -785,6 +776,15 @@
   </si>
   <si>
     <t>LED 3mm Dome Bicolor</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
   </si>
 </sst>
 </file>
@@ -1699,7 +1699,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1734,16 +1734,16 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>22</v>
@@ -1757,16 +1757,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>22</v>
@@ -1777,22 +1777,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1803,16 +1803,16 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>22</v>
@@ -1823,22 +1823,22 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1846,19 +1846,19 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>22</v>
@@ -1869,13 +1869,13 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -1884,7 +1884,7 @@
         <v>22</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1895,16 +1895,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>22</v>
@@ -1918,19 +1918,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1938,22 +1938,22 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1964,19 +1964,19 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1987,19 +1987,19 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2013,16 +2013,16 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2030,22 +2030,22 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" t="s">
         <v>93</v>
       </c>
-      <c r="C16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" t="s">
-        <v>95</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2059,13 +2059,13 @@
         <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
         <v>20</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>23</v>
@@ -2076,22 +2076,22 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2099,22 +2099,22 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C19" t="s">
-        <v>135</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2122,22 +2122,22 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2145,22 +2145,22 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="E21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2168,13 +2168,13 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
         <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
@@ -2183,7 +2183,7 @@
         <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2191,22 +2191,22 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2214,22 +2214,22 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2237,10 +2237,10 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -2249,10 +2249,10 @@
         <v>17</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="J25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2260,19 +2260,19 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E27" t="s">
         <v>60</v>
       </c>
-      <c r="C27" t="s">
+      <c r="F27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="J27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2280,19 +2280,19 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" t="s">
         <v>64</v>
       </c>
-      <c r="C28" t="s">
+      <c r="F28" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E28" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="J28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2300,19 +2300,19 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" t="s">
         <v>68</v>
       </c>
-      <c r="C29" t="s">
+      <c r="F29" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E29" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="J29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2329,13 +2329,13 @@
         <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="J31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2343,19 +2343,19 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
         <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="J32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2366,16 +2366,16 @@
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2383,19 +2383,19 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" t="s">
         <v>73</v>
       </c>
-      <c r="C34" t="s">
+      <c r="F34" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E34" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="J34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2403,7 +2403,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B36" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2411,7 +2411,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2419,22 +2419,22 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2447,37 +2447,37 @@
     <hyperlink ref="F14" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="F15" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
     <hyperlink ref="F22" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F31" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F32" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="F9" r:id="rId11" xr:uid="{E7FE330F-8A3B-4669-8B30-2C9E9A5FC581}"/>
-    <hyperlink ref="F18" r:id="rId12" xr:uid="{D29AE626-DF4E-4773-AA8D-0524E4224C52}"/>
-    <hyperlink ref="J11" r:id="rId13" xr:uid="{DAB40736-F04B-49BE-B956-976DD3855565}"/>
-    <hyperlink ref="F11" r:id="rId14" xr:uid="{5B664CC3-E913-48D8-8E4C-C36CC978BC62}"/>
-    <hyperlink ref="F12" r:id="rId15" xr:uid="{9A2C0F42-F9A7-41AA-94D5-CCEE60DCDB6C}"/>
-    <hyperlink ref="F19" r:id="rId16" xr:uid="{0D90FBA3-232B-45F3-9B80-144E63D03E3D}"/>
-    <hyperlink ref="F20" r:id="rId17" xr:uid="{8DF1F044-558D-44D8-8070-099BFF365FAB}"/>
-    <hyperlink ref="J24" r:id="rId18" xr:uid="{8B9632A9-814A-4DC4-9631-57B7806D3330}"/>
-    <hyperlink ref="F27" r:id="rId19" xr:uid="{D392D526-59B2-4A93-A093-DCD2091DFEBD}"/>
-    <hyperlink ref="F28" r:id="rId20" xr:uid="{008E511C-47F5-4260-BD59-24F612C3A54C}"/>
-    <hyperlink ref="F29" r:id="rId21" xr:uid="{B7BABB34-FFAC-4368-AC9C-3711E18528C8}"/>
-    <hyperlink ref="F34" r:id="rId22" xr:uid="{D0673C57-FA09-40F3-A004-4F5B32DB700F}"/>
-    <hyperlink ref="J8" r:id="rId23" xr:uid="{0A8324C1-BE5A-439C-A2BE-1A9CE9E466C8}"/>
-    <hyperlink ref="F23" r:id="rId24" xr:uid="{7E74E579-8BBC-460D-8171-1DD7E7105ABE}"/>
-    <hyperlink ref="J6" r:id="rId25" xr:uid="{E60E51FB-EE57-496C-BB85-FFD311DB3DAD}"/>
-    <hyperlink ref="F16" r:id="rId26" xr:uid="{A73CC50D-6402-4B9F-BA89-B7BEF6A9A237}"/>
-    <hyperlink ref="F5" r:id="rId27" xr:uid="{1A1C1243-6CD0-4D71-BF93-FB319C2C1DCC}"/>
-    <hyperlink ref="F7" r:id="rId28" xr:uid="{5387E2DD-7E16-4507-B60B-B69362367297}"/>
-    <hyperlink ref="F25" r:id="rId29" xr:uid="{E60A799E-C70E-4656-8426-1D272A3F13D2}"/>
-    <hyperlink ref="F33" r:id="rId30" xr:uid="{4F25721E-C4C9-49DB-97FF-D9D5C33601A0}"/>
-    <hyperlink ref="F21" r:id="rId31" xr:uid="{360AA49B-942A-4136-9898-3D7645969441}"/>
-    <hyperlink ref="F3" r:id="rId32" xr:uid="{B6FB057F-DC4C-4EFA-939D-705FFE5CCBEB}"/>
-    <hyperlink ref="F4" r:id="rId33" xr:uid="{5B69DA51-349B-4BAC-B42E-72EDB3822F52}"/>
-    <hyperlink ref="F6" r:id="rId34" xr:uid="{079911ED-A73D-4227-BB82-AF6A4545BD22}"/>
-    <hyperlink ref="F8" r:id="rId35" xr:uid="{F138ACE3-1C0B-4DA4-83B4-68E04D42124F}"/>
-    <hyperlink ref="F10" r:id="rId36" xr:uid="{9ED1FABF-4E47-46F6-A286-3E2431D22EF2}"/>
-    <hyperlink ref="F17" r:id="rId37" xr:uid="{1939E0C4-76A7-49EB-AB43-10430132F3D5}"/>
-    <hyperlink ref="F24" r:id="rId38" xr:uid="{F7765BE8-182D-4ED2-872D-B59FFBEDDC87}"/>
-    <hyperlink ref="J9" r:id="rId39" xr:uid="{B9E0B8B4-C7AA-4C36-B6A7-FDC9645CF2E1}"/>
+    <hyperlink ref="F9" r:id="rId9" xr:uid="{E7FE330F-8A3B-4669-8B30-2C9E9A5FC581}"/>
+    <hyperlink ref="F18" r:id="rId10" xr:uid="{D29AE626-DF4E-4773-AA8D-0524E4224C52}"/>
+    <hyperlink ref="J11" r:id="rId11" xr:uid="{DAB40736-F04B-49BE-B956-976DD3855565}"/>
+    <hyperlink ref="F11" r:id="rId12" xr:uid="{5B664CC3-E913-48D8-8E4C-C36CC978BC62}"/>
+    <hyperlink ref="F12" r:id="rId13" xr:uid="{9A2C0F42-F9A7-41AA-94D5-CCEE60DCDB6C}"/>
+    <hyperlink ref="F19" r:id="rId14" xr:uid="{0D90FBA3-232B-45F3-9B80-144E63D03E3D}"/>
+    <hyperlink ref="F20" r:id="rId15" xr:uid="{8DF1F044-558D-44D8-8070-099BFF365FAB}"/>
+    <hyperlink ref="J24" r:id="rId16" xr:uid="{8B9632A9-814A-4DC4-9631-57B7806D3330}"/>
+    <hyperlink ref="F27" r:id="rId17" xr:uid="{D392D526-59B2-4A93-A093-DCD2091DFEBD}"/>
+    <hyperlink ref="F28" r:id="rId18" xr:uid="{008E511C-47F5-4260-BD59-24F612C3A54C}"/>
+    <hyperlink ref="F29" r:id="rId19" xr:uid="{B7BABB34-FFAC-4368-AC9C-3711E18528C8}"/>
+    <hyperlink ref="F34" r:id="rId20" xr:uid="{D0673C57-FA09-40F3-A004-4F5B32DB700F}"/>
+    <hyperlink ref="J8" r:id="rId21" xr:uid="{0A8324C1-BE5A-439C-A2BE-1A9CE9E466C8}"/>
+    <hyperlink ref="F23" r:id="rId22" xr:uid="{7E74E579-8BBC-460D-8171-1DD7E7105ABE}"/>
+    <hyperlink ref="J6" r:id="rId23" xr:uid="{E60E51FB-EE57-496C-BB85-FFD311DB3DAD}"/>
+    <hyperlink ref="F16" r:id="rId24" xr:uid="{A73CC50D-6402-4B9F-BA89-B7BEF6A9A237}"/>
+    <hyperlink ref="F5" r:id="rId25" xr:uid="{1A1C1243-6CD0-4D71-BF93-FB319C2C1DCC}"/>
+    <hyperlink ref="F7" r:id="rId26" xr:uid="{5387E2DD-7E16-4507-B60B-B69362367297}"/>
+    <hyperlink ref="F33" r:id="rId27" xr:uid="{4F25721E-C4C9-49DB-97FF-D9D5C33601A0}"/>
+    <hyperlink ref="F21" r:id="rId28" xr:uid="{360AA49B-942A-4136-9898-3D7645969441}"/>
+    <hyperlink ref="F3" r:id="rId29" xr:uid="{B6FB057F-DC4C-4EFA-939D-705FFE5CCBEB}"/>
+    <hyperlink ref="F4" r:id="rId30" xr:uid="{5B69DA51-349B-4BAC-B42E-72EDB3822F52}"/>
+    <hyperlink ref="F6" r:id="rId31" xr:uid="{079911ED-A73D-4227-BB82-AF6A4545BD22}"/>
+    <hyperlink ref="F8" r:id="rId32" xr:uid="{F138ACE3-1C0B-4DA4-83B4-68E04D42124F}"/>
+    <hyperlink ref="F10" r:id="rId33" xr:uid="{9ED1FABF-4E47-46F6-A286-3E2431D22EF2}"/>
+    <hyperlink ref="F17" r:id="rId34" xr:uid="{1939E0C4-76A7-49EB-AB43-10430132F3D5}"/>
+    <hyperlink ref="F24" r:id="rId35" xr:uid="{F7765BE8-182D-4ED2-872D-B59FFBEDDC87}"/>
+    <hyperlink ref="J9" r:id="rId36" xr:uid="{B9E0B8B4-C7AA-4C36-B6A7-FDC9645CF2E1}"/>
+    <hyperlink ref="F25" r:id="rId37" xr:uid="{4D736825-2A97-41FE-A7B5-795799BFD9B1}"/>
+    <hyperlink ref="F31" r:id="rId38" xr:uid="{9125A19E-60DC-41ED-8B59-02FA8D835BBD}"/>
+    <hyperlink ref="F32" r:id="rId39" xr:uid="{AFECC905-17BF-4E19-B727-85620D8F1854}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
